--- a/wines.xlsx
+++ b/wines.xlsx
@@ -2987,940 +2987,3908 @@
       <c r="K43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="n"/>
-      <c r="J44" s="6" t="n"/>
-      <c r="K44" s="6" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 생 마르탱</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Saint Martin</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>도멘 라로슈</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Laroche</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>5만원대</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
-      <c r="J45" s="6" t="n"/>
-      <c r="K45" s="6" t="n"/>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 프르미에 크뤼 라 포레</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Chablis 1er Cru La Forest</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>도멘 뱅상 도비사</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Vincent Dauvissat</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>30만원대</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 최정상 생산자 중 하나</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="n"/>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="6" t="n"/>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 그랑 크뤼 부그로</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Grand Cru Bougros</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>도멘 윌리엄 페브르</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>William Fèvre</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Grand Cru</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>20만원대</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
-      <c r="I47" s="6" t="n"/>
-      <c r="J47" s="6" t="n"/>
-      <c r="K47" s="6" t="n"/>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 그랑 크뤼 라 무톤</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Grand Cru La Moutonne</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>도멘 롱-데파키</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Long-Depaquit</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Grand Cru</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>25만원대</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>그랑 크뤼 사이에 걸친 모노폴 밭</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n"/>
-      <c r="J48" s="6" t="n"/>
-      <c r="K48" s="6" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 생트 클레르</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Sainte Claire</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>장-마르크 브로카르</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Jean-Marc Brocard</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>4만원대</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="I49" s="6" t="n"/>
-      <c r="J49" s="6" t="n"/>
-      <c r="K49" s="6" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 프르미에 크뤼 몽맹</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Chablis 1er Cru Montmains</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>루이 미셸 에 피스</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Louis Michel &amp; Fils</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>오크 없이 순수한 미네랄 스타일</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>샤블리 그랑 크뤼 샤토 그르누유</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Grand Cru Château Grenouilles</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>라 샤블리지엔</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>La Chablisienne</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>샤블리</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Chablis Grand Cru</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>샹베르탱-클로 드 베즈 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Chambertin-Clos de Bèze Grand Cru</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>도멘 페블레</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Faiveley</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Chambertin-Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>100만원대</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="6" t="n"/>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>클로 드 타르 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Clos de Tart Grand Cru</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>도멘 뒤 클로 드 타르</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Domaine du Clos de Tart</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Clos de Tart</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>120만원대</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>단독 소유(모노폴) 그랑 크뤼</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="n"/>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>뮈지니 비에유 비뉴 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Musigny Vieilles Vignes Grand Cru</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>도멘 콩트 조르주 드 보귀에</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Comte Georges de Vogüé</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Musigny</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>200만원대</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
-      <c r="I54" s="6" t="n"/>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>샹볼-뮈지니 프르미에 크뤼 레 자무레즈</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny 1er Cru Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>도멘 자크-프레데릭 뮈니에</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Jacques-Frédéric Mugnier</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>300만원대</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6" t="n"/>
-      <c r="J55" s="6" t="n"/>
-      <c r="K55" s="6" t="n"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>클로 드 부조 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Clos de Vougeot Grand Cru</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>도멘 그로 프레르 에 쇠르</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Gros Frère et Sœur</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Clos de Vougeot</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>40만원대</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
-      <c r="I56" s="6" t="n"/>
-      <c r="J56" s="6" t="n"/>
-      <c r="K56" s="6" t="n"/>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>라 로마네 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>La Romanée Grand Cru</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>도멘 뒤 콩트 리제-벨레르</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Comte Liger-Belair</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>La Romanée</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>600만원대</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>프랑스에서 가장 작은 AOC(모노폴)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
-      <c r="I57" s="6" t="n"/>
-      <c r="J57" s="6" t="n"/>
-      <c r="K57" s="6" t="n"/>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>본-로마네</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Vosne-Romanée</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>도멘 실뱅 카티아르</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Sylvain Cathiard</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Vosne-Romanée</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>50만원대</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
-      <c r="I58" s="6" t="n"/>
-      <c r="J58" s="6" t="n"/>
-      <c r="K58" s="6" t="n"/>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>클로 드 라 로슈 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Clos de la Roche Grand Cru</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>도멘 뒤작</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Dujac</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Clos de la Roche</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>150만원대</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6" t="n"/>
-      <c r="J59" s="6" t="n"/>
-      <c r="K59" s="6" t="n"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>클로 드 라 로슈 비에유 비뉴 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Clos de la Roche Vieilles Vignes Grand Cru</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>도멘 퐁소</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Ponsot</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Clos de la Roche</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>120만원대</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>샹베르탱 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Chambertin Grand Cru</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>도멘 트라페 페르 에 피스</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Trapet Père et Fils</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Chambertin</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>100만원대</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
-      <c r="I61" s="6" t="n"/>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="6" t="n"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>주브레-샹베르탱</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Gevrey-Chambertin</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>도멘 클로드 뒤가</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Claude Dugat</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Gevrey-Chambertin</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>30만원대</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
-      <c r="I62" s="6" t="n"/>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="6" t="n"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>주브레-샹베르탱 비에유 비뉴</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Gevrey-Chambertin Vieilles Vignes</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>도멘 푸리에</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Fourrier</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Gevrey-Chambertin</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>30만원대</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
-      <c r="I63" s="6" t="n"/>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="6" t="n"/>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>뉘-생-조르주 프르미에 크뤼 클로 데 포레 생-조르주</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Nuits-Saint-Georges 1er Cru Clos des Forêts Saint-Georges</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>도멘 드 라를로</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de l'Arlot</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Nuits-Saint-Georges</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>25만원대</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="6" t="n"/>
-      <c r="I64" s="6" t="n"/>
-      <c r="J64" s="6" t="n"/>
-      <c r="K64" s="6" t="n"/>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>모레-생-드니</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Morey-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>도멘 페로-미노</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Perrot-Minot</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 뉘</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Morey-Saint-Denis</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>20만원대</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="6" t="n"/>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>본 그레브 비뉴 드 랑팡 제쥐</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Beaune Grèves Vigne de l'Enfant Jésus</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>부샤르 페르 에 피스</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Bouchard Père &amp; Fils</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Beaune</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>30만원대</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>코르통-샤를마뉴 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Corton-Charlemagne Grand Cru</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>루이 자도</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Louis Jadot</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Corton-Charlemagne</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>40만원대</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="6" t="n"/>
-      <c r="I67" s="6" t="n"/>
-      <c r="J67" s="6" t="n"/>
-      <c r="K67" s="6" t="n"/>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>샤토 코르통 그랑세 그랑 크뤼</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Château Corton Grancey Grand Cru</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>루이 라투르</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Louis Latour</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Corton</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>30만원대</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="6" t="n"/>
-      <c r="I68" s="6" t="n"/>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="6" t="n"/>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>뫼르소 프르미에 크뤼 페리에르</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Meursault 1er Cru Perrières</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>도멘 데 콩트 라퐁</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Domaine des Comtes Lafon</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Meursault</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>100만원대</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
-      <c r="I69" s="6" t="n"/>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="6" t="n"/>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>뫼르소</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Meursault</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>도멘 루로</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Roulot</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Meursault</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>50만원대</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
-      <c r="I70" s="6" t="n"/>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="6" t="n"/>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>샤사뉴-몽라셰</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Chassagne-Montrachet</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>도멘 라모네</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Ramonet</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Chassagne-Montrachet</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>30만원대</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
-      <c r="I71" s="6" t="n"/>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="6" t="n"/>
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>샤사뉴-몽라셰</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Chassagne-Montrachet</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>도멘 폴 피요</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Paul Pillot</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Chassagne-Montrachet</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>20만원대</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="6" t="n"/>
-      <c r="I72" s="6" t="n"/>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="6" t="n"/>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>퓔리니-몽라셰</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Puligny-Montrachet</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>올리비에 르플레브</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Olivier Leflaive</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Puligny-Montrachet</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="n"/>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n"/>
-      <c r="I73" s="6" t="n"/>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>퓔리니-몽라셰</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Puligny-Montrachet</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>도멘 르플레브</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Leflaive</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Puligny-Montrachet</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>40만원대</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="6" t="n"/>
-      <c r="I74" s="6" t="n"/>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="6" t="n"/>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>볼네 프르미에 크뤼 클로 데 뒥</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Volnay 1er Cru Clos des Ducs</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>도멘 마르키 당제르빌</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Marquis d'Angerville</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Volnay</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>50만원대</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>단독 소유(모노폴) 프르미에 크뤼</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="6" t="n"/>
-      <c r="I75" s="6" t="n"/>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="n"/>
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>볼네</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Volnay</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>도멘 드 몽티유</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de Montille</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Volnay</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n"/>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="6" t="n"/>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="6" t="n"/>
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>사비니-레-본</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Savigny-lès-Beaune</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>도멘 샹동 드 브리아이</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Chandon de Briailles</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Savigny-lès-Beaune</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>10만원대</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
-      <c r="I77" s="6" t="n"/>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="6" t="n"/>
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>쇼레-레-본</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Chorey-lès-Beaune</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>도멘 톨로-보</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Tollot-Beaut</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Chorey-lès-Beaune</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n"/>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="6" t="n"/>
-      <c r="I78" s="6" t="n"/>
-      <c r="J78" s="6" t="n"/>
-      <c r="K78" s="6" t="n"/>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>본 프르미에 크뤼 클로 데 무슈</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Beaune 1er Cru Clos des Mouches</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>메종 조제프 드루앵</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Joseph Drouhin</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 본</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Beaune</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>25만원대</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="n"/>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="6" t="n"/>
-      <c r="D79" s="6" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="6" t="n"/>
-      <c r="H79" s="6" t="n"/>
-      <c r="I79" s="6" t="n"/>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="6" t="n"/>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>메르퀴레 라 프랑부아지에르</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Mercurey La Framboisière</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>도멘 페블레</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Domaine Faiveley</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Mercurey</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>7만원대</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="6" t="n"/>
-      <c r="I80" s="6" t="n"/>
-      <c r="J80" s="6" t="n"/>
-      <c r="K80" s="6" t="n"/>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>메르퀴레 프르미에 크뤼 클로 데 바로</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Mercurey 1er Cru Clos des Barraults</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>도멘 미셸 쥐요</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Michel Juillot</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Mercurey</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>9만원대</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="n"/>
-      <c r="E81" s="6" t="n"/>
-      <c r="F81" s="6" t="n"/>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="6" t="n"/>
-      <c r="I81" s="6" t="n"/>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="6" t="n"/>
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>메르퀴레 비에유 비뉴</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Mercurey Vieilles Vignes</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>도멘 프랑수아 라키에</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>François Raquillet</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Mercurey</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>7만원대</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="n"/>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6" t="n"/>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="6" t="n"/>
-      <c r="G82" s="6" t="n"/>
-      <c r="H82" s="6" t="n"/>
-      <c r="I82" s="6" t="n"/>
-      <c r="J82" s="6" t="n"/>
-      <c r="K82" s="6" t="n"/>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>륄리 프르미에 크뤼</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Rully 1er Cru</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>도멘 뱅상 뒤레이유-장티알</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Vincent Dureuil-Janthial</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Rully</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>12만원대</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈 최고 평가 생산자 중 하나</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="n"/>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="6" t="n"/>
-      <c r="D83" s="6" t="n"/>
-      <c r="E83" s="6" t="n"/>
-      <c r="F83" s="6" t="n"/>
-      <c r="G83" s="6" t="n"/>
-      <c r="H83" s="6" t="n"/>
-      <c r="I83" s="6" t="n"/>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="6" t="n"/>
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>몽타니 프르미에 크뤼 라 그랑드 로슈</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Montagny 1er Cru La Grande Roche</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>루이 라투르</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Louis Latour</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Montagny</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>6만원대</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n"/>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="6" t="n"/>
-      <c r="G84" s="6" t="n"/>
-      <c r="H84" s="6" t="n"/>
-      <c r="I84" s="6" t="n"/>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="6" t="n"/>
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>부르고뉴 코트 샬로네즈 라 디고안</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Bourgogne Côte Chalonnaise La Digoine</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>도멘 드 빌렌</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Domaine de Villaine</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>코트 샬로네즈</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>레드</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="6" t="n"/>
-      <c r="I85" s="6" t="n"/>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>푸이-퓌세</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>도멘 J.A. 페레</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Domaine J.A. Ferret</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>푸이-퓌세의 역사적 명가</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="6" t="n"/>
-      <c r="I86" s="6" t="n"/>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="6" t="n"/>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>푸이-퓌세 비에유 비뉴</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé Vieilles Vignes</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>샤토-퓌세</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Château-Fuissé</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>9만원대</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="6" t="n"/>
-      <c r="I87" s="6" t="n"/>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="6" t="n"/>
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>푸이-퓌세</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>도멘 기팡-에낭</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Guffens-Heynen</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="6" t="n"/>
-      <c r="I88" s="6" t="n"/>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="6" t="n"/>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>마콩-빌라주</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Mâcon-Villages</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>메종 베르제</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Maison Verget</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Mâcon-Villages</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>4만원대</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="6" t="n"/>
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>푸이-뱅젤 레 카르</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Vinzelles Les Quarts</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>브레 브라더스</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Bret Brothers</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Vinzelles</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="6" t="n"/>
-      <c r="H90" s="6" t="n"/>
-      <c r="I90" s="6" t="n"/>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="6" t="n"/>
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>푸이-뱅젤</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Vinzelles</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>도멘 라 수프랑디에르</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>La Soufrandière</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Vinzelles</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>6만원대</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n"/>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="6" t="n"/>
-      <c r="D91" s="6" t="n"/>
-      <c r="E91" s="6" t="n"/>
-      <c r="F91" s="6" t="n"/>
-      <c r="G91" s="6" t="n"/>
-      <c r="H91" s="6" t="n"/>
-      <c r="I91" s="6" t="n"/>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="6" t="n"/>
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>푸이-퓌세</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>도멘 코르디에</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Cordier Père et Fils</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Pouilly-Fuissé</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>7만원대</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="6" t="n"/>
-      <c r="I92" s="6" t="n"/>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="6" t="n"/>
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>마콩 미이-라마르틴</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Mâcon Milly-Lamartine</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>레 제리티에 뒤 콩트 라퐁</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Les Héritiers du Comte Lafon</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>마코네</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Mâcon</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>화이트</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>5만원대</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="n"/>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6" t="n"/>
-      <c r="E93" s="6" t="n"/>
-      <c r="F93" s="6" t="n"/>
-      <c r="G93" s="6" t="n"/>
-      <c r="H93" s="6" t="n"/>
-      <c r="I93" s="6" t="n"/>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="6" t="n"/>
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>크리스탈</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Cristal</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>루이 로드레</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Louis Roederer</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>몽타뉴 드 랭스</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>40만원대</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>러시아 황제를 위해 만들어진 프레스티지 퀴베</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="6" t="n"/>
-      <c r="I94" s="6" t="n"/>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="6" t="n"/>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>뤼나르 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Ruinart Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>뤼나르</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Ruinart</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>몽타뉴 드 랭스</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>13만원대</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>현존 최고(最古) 샴페인 하우스</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="n"/>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="6" t="n"/>
-      <c r="G95" s="6" t="n"/>
-      <c r="H95" s="6" t="n"/>
-      <c r="I95" s="6" t="n"/>
-      <c r="J95" s="6" t="n"/>
-      <c r="K95" s="6" t="n"/>
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>멈 코르동 루즈</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Mumm Cordon Rouge</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>G.H. 멈</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>G.H. Mumm</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>몽타뉴 드 랭스</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>6만원대</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="6" t="n"/>
-      <c r="G96" s="6" t="n"/>
-      <c r="H96" s="6" t="n"/>
-      <c r="I96" s="6" t="n"/>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="6" t="n"/>
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>파이퍼-하이직 퀴베 브뤼</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Piper-Heidsieck Cuvée Brut</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>파이퍼-하이직</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Piper-Heidsieck</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>몽타뉴 드 랭스</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>5만원대</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="n"/>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="6" t="n"/>
-      <c r="H97" s="6" t="n"/>
-      <c r="I97" s="6" t="n"/>
-      <c r="J97" s="6" t="n"/>
-      <c r="K97" s="6" t="n"/>
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>앙리오 브뤼 수버랭</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Henriot Brut Souverain</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>앙리오</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Henriot</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>몽타뉴 드 랭스</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>7만원대</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
-      <c r="G98" s="6" t="n"/>
-      <c r="H98" s="6" t="n"/>
-      <c r="I98" s="6" t="n"/>
-      <c r="J98" s="6" t="n"/>
-      <c r="K98" s="6" t="n"/>
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>샤르토뉴-타이에 퀴베 생트-안</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Chartogne-Taillet Cuvée Sainte-Anne</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>샤르토뉴-타이에</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Chartogne-Taillet</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>몽타뉴 드 랭스</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>9만원대</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>주목받는 소규모 생산자(그로워)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="n"/>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="6" t="n"/>
-      <c r="I99" s="6" t="n"/>
-      <c r="J99" s="6" t="n"/>
-      <c r="K99" s="6" t="n"/>
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>폴 로저 브뤼 레제르브</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Pol Roger Brut Réserve</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>폴 로저</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Pol Roger</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>9만원대</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>처칠이 사랑한 샴페인</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
-      <c r="I100" s="6" t="n"/>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="6" t="n"/>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>벨 에포크</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Belle Epoque</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>페리에-주에</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Perrier-Jouët</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>25만원대</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>아네모네 꽃병으로 유명한 프레스티지 퀴베</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="n"/>
-      <c r="B101" s="6" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="6" t="n"/>
-      <c r="F101" s="6" t="n"/>
-      <c r="G101" s="6" t="n"/>
-      <c r="H101" s="6" t="n"/>
-      <c r="I101" s="6" t="n"/>
-      <c r="J101" s="6" t="n"/>
-      <c r="K101" s="6" t="n"/>
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>고세 그랑드 레제르브</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Gosset Grande Réserve</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>고세</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Gosset</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>9만원대</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6" t="n"/>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="6" t="n"/>
-      <c r="I102" s="6" t="n"/>
-      <c r="J102" s="6" t="n"/>
-      <c r="K102" s="6" t="n"/>
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>클로 데 구아세</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Clos des Goisses</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>필리포나</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Philipponnat</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>40만원대</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>샹파뉴 최초의 단일 밭(클로) 샴페인</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="n"/>
-      <c r="B103" s="6" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="D103" s="6" t="n"/>
-      <c r="E103" s="6" t="n"/>
-      <c r="F103" s="6" t="n"/>
-      <c r="G103" s="6" t="n"/>
-      <c r="H103" s="6" t="n"/>
-      <c r="I103" s="6" t="n"/>
-      <c r="J103" s="6" t="n"/>
-      <c r="K103" s="6" t="n"/>
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>앙리 지로 오마주 오 피노 누아</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Henri Giraud Hommage au Pinot Noir</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>앙리 지로</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Henri Giraud</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>아이(Aÿ) 그랑 크뤼 명가</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-      <c r="E104" s="6" t="n"/>
-      <c r="F104" s="6" t="n"/>
-      <c r="G104" s="6" t="n"/>
-      <c r="H104" s="6" t="n"/>
-      <c r="I104" s="6" t="n"/>
-      <c r="J104" s="6" t="n"/>
-      <c r="K104" s="6" t="n"/>
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>가티누아 아이 그랑 크뤼 브뤼</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Gatinois Aÿ Grand Cru Brut</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>가티누아</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Gatinois</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>9만원대</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="6" t="n"/>
-      <c r="C105" s="6" t="n"/>
-      <c r="D105" s="6" t="n"/>
-      <c r="E105" s="6" t="n"/>
-      <c r="F105" s="6" t="n"/>
-      <c r="G105" s="6" t="n"/>
-      <c r="H105" s="6" t="n"/>
-      <c r="I105" s="6" t="n"/>
-      <c r="J105" s="6" t="n"/>
-      <c r="K105" s="6" t="n"/>
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>조르주 라발 퀴미에르 프르미에 크뤼</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Georges Laval Cumières 1er Cru</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>조르주 라발</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Georges Laval</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>발레 드 라 마른</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤르도네, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>25만원대</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>유기농 선구자 그로워</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="n"/>
-      <c r="B106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="6" t="n"/>
-      <c r="I106" s="6" t="n"/>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="6" t="n"/>
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>이니시알 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Initial Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>자크 셀로스</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Jacques Selosse</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 블랑</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>60만원대</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>그로워 샴페인 운동의 전설</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="n"/>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
-      <c r="G107" s="6" t="n"/>
-      <c r="H107" s="6" t="n"/>
-      <c r="I107" s="6" t="n"/>
-      <c r="J107" s="6" t="n"/>
-      <c r="K107" s="6" t="n"/>
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>라티튜드 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Latitude Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>라르망디에-베르니에</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Larmandier-Bernier</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 블랑</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>10만원대</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>비오디나미 농법 그로워</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="n"/>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="6" t="n"/>
-      <c r="H108" s="6" t="n"/>
-      <c r="I108" s="6" t="n"/>
-      <c r="J108" s="6" t="n"/>
-      <c r="K108" s="6" t="n"/>
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>기 샤를마뉴 레제르브 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Guy Charlemagne Réserve Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>기 샤를마뉴</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Guy Charlemagne</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 블랑</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="n"/>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
-      <c r="G109" s="6" t="n"/>
-      <c r="H109" s="6" t="n"/>
-      <c r="I109" s="6" t="n"/>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="6" t="n"/>
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>들라모트 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Delamotte Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>들라모트</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Delamotte</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 블랑</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>12만원대</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>살롱의 자매 하우스</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="n"/>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="6" t="n"/>
-      <c r="H110" s="6" t="n"/>
-      <c r="I110" s="6" t="n"/>
-      <c r="J110" s="6" t="n"/>
-      <c r="K110" s="6" t="n"/>
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>드 수자 트라디시옹 브뤼</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>De Sousa Tradition Brut</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>드 수자</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>De Sousa</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 블랑</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네, 피노 누아, 피노 뫼니에</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>8만원대</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="n"/>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
-      <c r="G111" s="6" t="n"/>
-      <c r="H111" s="6" t="n"/>
-      <c r="I111" s="6" t="n"/>
-      <c r="J111" s="6" t="n"/>
-      <c r="K111" s="6" t="n"/>
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>레 피에리에르 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Les Pierrières Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>울리스 콜랭</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Ulysse Collin</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>코트 드 세잔</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>25만원대</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="n"/>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="6" t="n"/>
-      <c r="F112" s="6" t="n"/>
-      <c r="G112" s="6" t="n"/>
-      <c r="H112" s="6" t="n"/>
-      <c r="I112" s="6" t="n"/>
-      <c r="J112" s="6" t="n"/>
-      <c r="K112" s="6" t="n"/>
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>몽괴 블랑 드 블랑</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Montgueux Blanc de Blancs</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>자크 라세뉴</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Jacques Lassaigne</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 바르</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>샤르도네</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>오브의 샤르도네 명산지 몽괴</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="n"/>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-      <c r="E113" s="6" t="n"/>
-      <c r="F113" s="6" t="n"/>
-      <c r="G113" s="6" t="n"/>
-      <c r="H113" s="6" t="n"/>
-      <c r="I113" s="6" t="n"/>
-      <c r="J113" s="6" t="n"/>
-      <c r="K113" s="6" t="n"/>
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>피에르 제르베 로리지날</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Pierre Gerbais L'Originale</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>피에르 제르베</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Pierre Gerbais</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 바르</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>피노 블랑</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>12만원대</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>희귀 품종 피노 블랑 100%</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="n"/>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="6" t="n"/>
-      <c r="I114" s="6" t="n"/>
-      <c r="J114" s="6" t="n"/>
-      <c r="K114" s="6" t="n"/>
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>마리 쿠르탱 레조낭스</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Marie Courtin Résonance</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>마리 쿠르탱</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Marie Courtin</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 바르</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>13만원대</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>단일 밭·단일 빈티지 철학의 그로워</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="n"/>
-      <c r="B115" s="6" t="n"/>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
-      <c r="E115" s="6" t="n"/>
-      <c r="F115" s="6" t="n"/>
-      <c r="G115" s="6" t="n"/>
-      <c r="H115" s="6" t="n"/>
-      <c r="I115" s="6" t="n"/>
-      <c r="J115" s="6" t="n"/>
-      <c r="K115" s="6" t="n"/>
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>뵈트 에 소르베 피데스</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Vouette et Sorbée Fidèle</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>뵈트 에 소르베</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Vouette et Sorbée</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>코트 데 바르</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>스파클링</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>15만원대</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>

--- a/wines.xlsx
+++ b/wines.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -70,8 +70,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -88,8 +94,13 @@
         <fgColor rgb="FFFFF6E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00722F4B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -112,11 +123,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C0CE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C0CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C0CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9C0CE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +153,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -493,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -669,6 +697,18 @@
       <c r="B21" s="7" t="inlineStr">
         <is>
           <t>품종 = 블렌드면 쉼표로 나열 권장 (예: 피노 누아, 샤르도네, 피노 뫼니에) — 검색에 유리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>사진 넣기</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>와인 사진을 wine-map/assets/wines 폴더에 넣고, 사진파일 칸에 파일명(예: krug.jpg)을 적으면 사이트에 표시됩니다. 비우면 타입별 보틀 그림이 나옵니다.</t>
         </is>
       </c>
     </row>
@@ -683,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K500"/>
+  <dimension ref="A1:L500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -697,6 +737,7 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,6 +794,11 @@
       <c r="K1" s="4" t="inlineStr">
         <is>
           <t>설명</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>사진파일</t>
         </is>
       </c>
     </row>

--- a/wines.xlsx
+++ b/wines.xlsx
@@ -6157,6 +6157,11 @@
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>gosset-gosset-grande-reserve.png</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
